--- a/PurchasePlan.xlsx
+++ b/PurchasePlan.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexklausing/Documents/family-hub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA9C6C23-6CDD-234C-A7DF-743EA93D0983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF176FE-0D70-CC49-93D9-DCD6B0B7C7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="680" windowWidth="28040" windowHeight="17140" xr2:uid="{C8E3985A-45D7-6049-B8BA-6DA90127AB9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>Raspberry Pi 5 4GB</t>
   </si>
@@ -90,13 +90,28 @@
   </si>
   <si>
     <t>Right-Angle Micro-HDMI to HDMI Cable (3 Feet)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Silicon-Power-256GB-Gen3x4-SP256GBP34A60M28/dp/B07ZGK3K4V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silicon Power 256GB NVMe M.2 PCIe Gen3x4 2280 SSD (SP256GBP34A60M28) </t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/M-2-PoE-HAT-Compatible-High-Speed/dp/B0DNLSZ3LF</t>
+  </si>
+  <si>
+    <t>ALSO CONSIDER BUT NOT IN CURRENT PURCHASE PLAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">| **NVMe PCIe Hat** | Waveshare PCIe to M.2 HAT+ (Model B) </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -113,6 +128,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -140,10 +169,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -479,155 +518,194 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79C3EC79-AD71-9E43-8B80-D2F51DF7D5C7}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="123" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="123" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="10.83203125" style="2"/>
+    <col min="5" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>110</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <f>B2</f>
         <v>110</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>10.95</v>
       </c>
-      <c r="D3">
-        <f t="shared" ref="D3:D5" si="0">B3</f>
+      <c r="D3" s="2">
+        <f t="shared" ref="D3:D4" si="0">B3</f>
         <v>10.95</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>19.95</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>19.95</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B4" s="2">
         <v>12.95</v>
       </c>
-      <c r="D5">
+      <c r="D4" s="2">
         <f t="shared" si="0"/>
         <v>12.95</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2">
+        <v>59.79</v>
+      </c>
+      <c r="D6" s="2">
+        <v>59.79</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2">
+        <v>30.99</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
+      <c r="B9" s="2">
         <v>339.99</v>
       </c>
-      <c r="D8">
-        <f t="shared" ref="D8:D10" si="1">C8+B8</f>
+      <c r="D9" s="2">
+        <f t="shared" ref="D9" si="1">C9+B9</f>
         <v>339.99</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D10">
+      <c r="D11" s="2">
         <v>20</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E11" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D12">
+      <c r="D13" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
+      <c r="E13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D14">
-        <f>SUM(D2:D13)</f>
-        <v>523.84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="C15" s="6"/>
+      <c r="D15" s="6">
+        <f>SUM(D2:D14)</f>
+        <v>594.67000000000007</v>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="2">
+        <v>19.95</v>
+      </c>
+      <c r="D27" s="2">
+        <f>B27</f>
+        <v>19.95</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B22">
+      <c r="B28" s="2">
         <v>345.99</v>
       </c>
-      <c r="C22">
+      <c r="C28" s="2">
         <v>120.4</v>
       </c>
-      <c r="D22" s="1"/>
-      <c r="E22" t="s">
+      <c r="D28" s="4"/>
+      <c r="E28" s="1" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{3C46E6C3-68E4-294C-A801-EFA628A05A61}"/>
-    <hyperlink ref="E3:E5" r:id="rId2" display="https://www.pishop.us/product/raspberry-pi-5-4gb/" xr:uid="{CF100F01-6370-2643-8FBA-F8DDDCE5B3C6}"/>
-    <hyperlink ref="E8" r:id="rId3" xr:uid="{78A37FF5-F345-D94C-87D6-8604F47B3A3E}"/>
+    <hyperlink ref="E3:E4" r:id="rId2" display="https://www.pishop.us/product/raspberry-pi-5-4gb/" xr:uid="{CF100F01-6370-2643-8FBA-F8DDDCE5B3C6}"/>
+    <hyperlink ref="E9" r:id="rId3" xr:uid="{78A37FF5-F345-D94C-87D6-8604F47B3A3E}"/>
+    <hyperlink ref="E7" r:id="rId4" xr:uid="{B2082589-475F-424E-82C3-07C95814CFFD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
